--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1457-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1457-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{50FE8C2C-E79C-4EAC-B904-7CFFE41D0BF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D13EB97F-7BFE-4FC7-9B24-54669F510C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{5B2C4A61-AD8C-497B-9067-295CDC682124}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{BF1F9CFE-29E5-4DA8-8ADD-B7F7582BE859}"/>
   </bookViews>
   <sheets>
     <sheet name="1457-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1532,30 +1532,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26D30B35-0560-4310-A630-805527EC297D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{899CE9E3-FA9F-4141-9599-DA0B21007578}">
   <dimension ref="A1:X44"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1589,7 +1589,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1625,7 +1625,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1745,7 +1745,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>6.43</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1889,7 +1889,7 @@
         <v>8.31</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="41"/>
       <c r="B7" s="42"/>
       <c r="C7" s="17" t="s">
@@ -1917,7 +1917,7 @@
       <c r="W7" s="48"/>
       <c r="X7" s="44"/>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="37">
         <v>2022</v>
       </c>
@@ -1989,7 +1989,7 @@
         <v>5.83</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="49">
         <v>2021</v>
       </c>
@@ -2061,7 +2061,7 @@
         <v>6.17</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="37">
         <v>2020</v>
       </c>
@@ -2133,7 +2133,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>33</v>
       </c>
@@ -2207,7 +2207,7 @@
         <v>7.19</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>33</v>
       </c>
@@ -2281,7 +2281,7 @@
         <v>5.36</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="49">
         <v>2019</v>
       </c>
@@ -2353,7 +2353,7 @@
         <v>9.36</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>33</v>
       </c>
@@ -2427,7 +2427,7 @@
         <v>5.36</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
         <v>33</v>
       </c>
@@ -2501,7 +2501,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <v>2018</v>
       </c>
@@ -2573,7 +2573,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="49">
         <v>2017</v>
       </c>
@@ -2645,7 +2645,7 @@
         <v>5.93</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="37">
         <v>2016</v>
       </c>
@@ -2717,7 +2717,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="49">
         <v>2015</v>
       </c>
@@ -2789,7 +2789,7 @@
         <v>6.35</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <v>2014</v>
       </c>
@@ -2861,7 +2861,7 @@
         <v>3.77</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="39">
         <v>2013</v>
       </c>
@@ -2933,7 +2933,7 @@
         <v>6.51</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="41"/>
       <c r="B22" s="42"/>
       <c r="C22" s="17" t="s">
@@ -2961,7 +2961,7 @@
       <c r="W22" s="48"/>
       <c r="X22" s="44"/>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>2012</v>
       </c>
@@ -3033,7 +3033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="49">
         <v>2011</v>
       </c>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2010</v>
       </c>
@@ -3177,7 +3177,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="49">
         <v>2009</v>
       </c>
@@ -3249,7 +3249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <v>2008</v>
       </c>
@@ -3321,7 +3321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="49">
         <v>2007</v>
       </c>
@@ -3393,7 +3393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>2006</v>
       </c>
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="49">
         <v>2005</v>
       </c>
@@ -3537,7 +3537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>2004</v>
       </c>
@@ -3609,7 +3609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="49">
         <v>2003</v>
       </c>
@@ -3681,7 +3681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37">
         <v>2002</v>
       </c>
@@ -3753,7 +3753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="49">
         <v>2001</v>
       </c>
@@ -3825,7 +3825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="37">
         <v>2000</v>
       </c>
@@ -3897,7 +3897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="49">
         <v>1999</v>
       </c>
@@ -3969,7 +3969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="37">
         <v>1998</v>
       </c>
@@ -4041,7 +4041,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="49">
         <v>1997</v>
       </c>
@@ -4113,7 +4113,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="37">
         <v>1996</v>
       </c>
@@ -4185,7 +4185,7 @@
         <v>9.35</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="49">
         <v>1995</v>
       </c>
@@ -4257,7 +4257,7 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="37">
         <v>1994</v>
       </c>
@@ -4329,7 +4329,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="49">
         <v>1993</v>
       </c>
@@ -4401,7 +4401,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="37">
         <v>1992</v>
       </c>
@@ -4473,7 +4473,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="49" t="s">
         <v>53</v>
       </c>
